--- a/仕様書&企画書/春チーム制作仕様書.xlsx
+++ b/仕様書&企画書/春チーム制作仕様書.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\0205h\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hakutokawanami\Desktop\github\Fall3\仕様書&amp;企画書\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8FBD9F83-051B-4EE8-884B-4FFA84CA17AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADAA1E83-B0EF-4C55-B560-98D9149AD400}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11190" yWindow="3540" windowWidth="12735" windowHeight="11295" xr2:uid="{C7FED82F-B019-48EF-8E25-359DD3736B63}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C7FED82F-B019-48EF-8E25-359DD3736B63}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
   <si>
     <t>プレイヤー</t>
     <phoneticPr fontId="1"/>
@@ -107,47 +107,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>弾はプレイヤーの向きに応じてｘ、ｙ軸にまっすぐ飛ぶ</t>
-  </si>
-  <si>
-    <t>弾が通った位置の床が破壊される</t>
-    <rPh sb="0" eb="1">
-      <t>タマ</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>トオ</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>イチ</t>
-    </rPh>
-    <rPh sb="8" eb="9">
-      <t>ユカ</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>ハカイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>必殺技を使ったプレイヤーが乗っている床は破壊されないように</t>
-    <rPh sb="0" eb="3">
-      <t>ヒッサツワザ</t>
-    </rPh>
-    <rPh sb="4" eb="5">
-      <t>ツカ</t>
-    </rPh>
-    <rPh sb="13" eb="14">
-      <t>ノ</t>
-    </rPh>
-    <rPh sb="18" eb="19">
-      <t>ユカ</t>
-    </rPh>
-    <rPh sb="20" eb="22">
-      <t>ハカイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>床</t>
     <rPh sb="0" eb="1">
       <t>ユカ</t>
@@ -260,6 +219,26 @@
   </si>
   <si>
     <t>（タイトルに戻ったら０にリセット）</t>
+  </si>
+  <si>
+    <t>弾はプレイヤーの向きに応じてまっすぐ飛んでいく</t>
+    <rPh sb="18" eb="19">
+      <t>ト</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>敵にあてたら吹っ飛ばす</t>
+    <rPh sb="0" eb="1">
+      <t>テキ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>フ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>ト</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
@@ -711,145 +690,143 @@
     </row>
     <row r="10" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C10" s="2" t="s">
-        <v>9</v>
+        <v>37</v>
       </c>
     </row>
     <row r="11" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C11" s="2" t="s">
-        <v>10</v>
+        <v>38</v>
       </c>
     </row>
     <row r="12" spans="2:3" x14ac:dyDescent="0.4">
-      <c r="C12" s="2" t="s">
-        <v>11</v>
-      </c>
+      <c r="C12" s="2"/>
     </row>
     <row r="14" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B14" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C15" s="2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="16" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C16" s="2" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="17" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C17" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B19" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C20" s="2" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C21" s="2" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="23" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B23" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B25" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="26" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C26" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="27" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C27" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="28" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C28" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="30" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B30" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="31" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C31" s="2" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="32" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C32" s="2" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="33" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C33" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B35" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="36" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C36" s="2" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="37" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C37" s="2" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="38" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C38" s="2" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
     </row>
     <row r="39" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C39" s="2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="40" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C40" s="2" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -868,17 +845,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="9ec34610-451d-4630-b8fd-572cd48b9242">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="6c2b5900-f3aa-4370-ae7f-2ba8f3ef8483" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x010100FA41B8A39F5D7C42A915EA3203D3475A" ma:contentTypeVersion="11" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="7e834b3ab6b14b21ce0dd1371c7b7ca6">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="9ec34610-451d-4630-b8fd-572cd48b9242" xmlns:ns3="6c2b5900-f3aa-4370-ae7f-2ba8f3ef8483" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="f1037d40a4279293769a11b6681ff777" ns2:_="" ns3:_="">
     <xsd:import namespace="9ec34610-451d-4630-b8fd-572cd48b9242"/>
@@ -1073,6 +1039,17 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="9ec34610-451d-4630-b8fd-572cd48b9242">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="6c2b5900-f3aa-4370-ae7f-2ba8f3ef8483" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B0EC6BCC-E260-4FFF-BA18-2AD4CE3774C4}">
   <ds:schemaRefs>
@@ -1082,23 +1059,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0DE6F05A-16B4-4CD5-A0B0-F7DBE57D4A27}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="6c2b5900-f3aa-4370-ae7f-2ba8f3ef8483"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="9ec34610-451d-4630-b8fd-572cd48b9242"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D44DDB74-8D16-488B-97CB-D111EE8DB5E7}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1115,4 +1075,21 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0DE6F05A-16B4-4CD5-A0B0-F7DBE57D4A27}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="6c2b5900-f3aa-4370-ae7f-2ba8f3ef8483"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="9ec34610-451d-4630-b8fd-572cd48b9242"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/仕様書&企画書/春チーム制作仕様書.xlsx
+++ b/仕様書&企画書/春チーム制作仕様書.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hakutokawanami\Desktop\github\Fall3\仕様書&amp;企画書\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADAA1E83-B0EF-4C55-B560-98D9149AD400}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{969010D8-1410-4F74-86F5-1716C8CC19EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C7FED82F-B019-48EF-8E25-359DD3736B63}"/>
   </bookViews>
@@ -321,6 +321,854 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>428625</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>381000</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="正方形/長方形 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6FC8BADC-093A-E2BB-E99F-63CDD4A80B19}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8448675" y="523875"/>
+          <a:ext cx="9553575" cy="6019800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>685799</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>371474</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="正方形/長方形 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{501283E9-23C6-1E9C-F79A-078907AB8308}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11449049" y="4200525"/>
+          <a:ext cx="3800475" cy="914400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent2"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent2"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="4000"/>
+            <a:t>ゲームスタート</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>371475</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="正方形/長方形 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9DFB2A2E-5B89-4C3B-83D6-D951603E5BC4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11449050" y="5381625"/>
+          <a:ext cx="3800475" cy="914400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent2"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent2"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="4400"/>
+            <a:t>ゲーム終了</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>428625</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>571500</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="正方形/長方形 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1174484E-3686-4D53-96E1-28C5DBA25781}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8448675" y="6010275"/>
+          <a:ext cx="2200275" cy="514350"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent2"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent2"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1800"/>
+            <a:t>勝利数リセット</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>323850</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>438150</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>209550</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6" name="正方形/長方形 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{02484B88-7CC6-4671-867C-884323676800}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11087100" y="1076325"/>
+          <a:ext cx="4229100" cy="2228850"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent2"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent2"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="7200"/>
+            <a:t>タイトル</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>200025</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>419100</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>209550</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7" name="スマイル 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DABE4BEC-B2B3-570F-53C0-0223ED89894F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8905875" y="1952625"/>
+          <a:ext cx="1590675" cy="1590675"/>
+        </a:xfrm>
+        <a:prstGeom prst="smileyFace">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent2"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent2"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>400050</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>619125</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="8" name="スマイル 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5C8D4C10-7D7E-4D34-873B-CD4BAABC7693}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="15963900" y="2000250"/>
+          <a:ext cx="1590675" cy="1590675"/>
+        </a:xfrm>
+        <a:prstGeom prst="smileyFace">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent2"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent2"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>152400</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="9" name="正方形/長方形 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AE087066-6050-4B7E-BE0A-6E2744F6FF36}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8715375" y="3829050"/>
+          <a:ext cx="2200275" cy="514350"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent2"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent2"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1800"/>
+            <a:t>　　　勝利数</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>66675</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>209550</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="10" name="正方形/長方形 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EA721A4C-D24A-4809-BD1E-B32EF3868416}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="15630525" y="3895725"/>
+          <a:ext cx="2200275" cy="514350"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent2"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent2"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1800"/>
+            <a:t>　　　勝利数</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>457200</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>409575</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="11" name="正方形/長方形 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C1301516-4889-4505-9340-8B2DB10996F0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8477250" y="6991350"/>
+          <a:ext cx="9553575" cy="6019800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>552450</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>238125</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="12" name="正方形/長方形 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{884D3DDE-E0BD-4A43-B730-96810B655A5A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11315700" y="10601325"/>
+          <a:ext cx="3800475" cy="914400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent2"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent2"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="4000"/>
+            <a:t>リスタート</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>561976</xdr:colOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>247651</xdr:colOff>
+      <xdr:row>53</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="13" name="正方形/長方形 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{19A529D0-79F1-4206-9AD2-BA0BD5CE3475}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11325226" y="11772900"/>
+          <a:ext cx="3800475" cy="914400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent2"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent2"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="4400"/>
+            <a:t>タイトル</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>228600</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>228600</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>142875</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="14" name="スマイル 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C8232017-7124-4BCF-80EC-19C061DAB2C3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10306050" y="8086725"/>
+          <a:ext cx="1971675" cy="1847850"/>
+        </a:xfrm>
+        <a:prstGeom prst="smileyFace">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent2"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent2"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>180975</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>219075</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>190499</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="16" name="正方形/長方形 15">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B4F70873-2748-446E-BFDA-E2B9C4F0914F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="13001625" y="8572500"/>
+          <a:ext cx="3467100" cy="1142999"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent2"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent2"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="4000"/>
+            <a:t>勝利数増える</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -832,6 +1680,7 @@
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -845,6 +1694,17 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="9ec34610-451d-4630-b8fd-572cd48b9242">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="6c2b5900-f3aa-4370-ae7f-2ba8f3ef8483" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x010100FA41B8A39F5D7C42A915EA3203D3475A" ma:contentTypeVersion="11" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="7e834b3ab6b14b21ce0dd1371c7b7ca6">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="9ec34610-451d-4630-b8fd-572cd48b9242" xmlns:ns3="6c2b5900-f3aa-4370-ae7f-2ba8f3ef8483" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="f1037d40a4279293769a11b6681ff777" ns2:_="" ns3:_="">
     <xsd:import namespace="9ec34610-451d-4630-b8fd-572cd48b9242"/>
@@ -1039,17 +1899,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="9ec34610-451d-4630-b8fd-572cd48b9242">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="6c2b5900-f3aa-4370-ae7f-2ba8f3ef8483" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B0EC6BCC-E260-4FFF-BA18-2AD4CE3774C4}">
   <ds:schemaRefs>
@@ -1059,6 +1908,23 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0DE6F05A-16B4-4CD5-A0B0-F7DBE57D4A27}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="6c2b5900-f3aa-4370-ae7f-2ba8f3ef8483"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="9ec34610-451d-4630-b8fd-572cd48b9242"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D44DDB74-8D16-488B-97CB-D111EE8DB5E7}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1075,21 +1941,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0DE6F05A-16B4-4CD5-A0B0-F7DBE57D4A27}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="6c2b5900-f3aa-4370-ae7f-2ba8f3ef8483"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="9ec34610-451d-4630-b8fd-572cd48b9242"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>